--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260811.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260811.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.24%</t>
+          <t>14.15%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.55%</t>
+          <t>12.34%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.96%</t>
+          <t>10.98%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>10.22%</t>
+          <t>10.26%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,198,800,000</t>
+          <t>1,208,950,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.83%</t>
+          <t>7.80%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>36,100,000</t>
+          <t>36,200,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.51%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>811,260,000</t>
+          <t>816,560,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.60%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
@@ -814,51 +814,51 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>247,714,000</t>
+          <t>116,200,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>112,800,000</t>
+          <t>247,714,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -902,73 +902,73 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>64,710,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>64,710,000</t>
+          <t>209,210,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>209,210,000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1029,29 +1029,29 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>82,480,000</t>
+          <t>83,480,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>119,300,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,51 +1063,51 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>119,300,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>8,504,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1117,51 +1117,51 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>412</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>76,770,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,468,000</t>
+          <t>76,770,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>8,504,000</t>
+          <t>12,468,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,66 +1195,66 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>34,120,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>34,120,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>27,842,899</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>27,842,899</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1327,39 +1327,39 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>4,224,938,626</t>
+          <t>4,615,334,210</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,873,640,721</t>
+          <t>1,894,926,117</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>-1,430,883,971</t>
+          <t>-1,924,070,867</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
